--- a/verification/cases/roundtrip/workbook_protection/init.xlsx
+++ b/verification/cases/roundtrip/workbook_protection/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58BF369B-13FC-44E6-8DB3-551054B01560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-20" windowWidth="24800" windowHeight="16600" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,8 +38,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
@@ -74,6 +80,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,11 +410,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" mc:Ignorable="mv" mc:PreserveAttributes="mv:*">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -409,11 +423,10 @@
       </c>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="10" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <pageSetup paperSize="10" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">
       <mx:PLV Mode="1" OnePage="0" WScale="0"/>
